--- a/cds_files/ArizonaState_CDS_2022-2023.xlsx
+++ b/cds_files/ArizonaState_CDS_2022-2023.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>0.712</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3</v>
+        <v>0.288</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>0.31</v>
       </c>
       <c r="C5" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
